--- a/diseases/d057/2026-2029.xlsx
+++ b/diseases/d057/2026-2029.xlsx
@@ -7910,12 +7910,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -7940,22 +7940,22 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>0.003267233630263065</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -7988,40 +7988,185 @@
       </c>
       <c r="AV51" t="inlineStr">
         <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA51" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB51" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC51" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>D057</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>sfts</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>SFTS</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>D057</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>SFTS</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>发热伴血小板减少综合征</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>1</v>
+      </c>
+      <c r="O52" t="n">
+        <v>1</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0.001937969923792046</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP52" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr"/>
+      <c r="AT52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV52" t="inlineStr">
+        <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW51" t="inlineStr">
+      <c r="AW52" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
+      <c r="AX52" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY51" t="inlineStr">
+      <c r="AY52" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
+      <c r="AZ52" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA51" t="inlineStr">
+      <c r="BA52" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB51" t="inlineStr">
+      <c r="BB52" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC51" t="inlineStr">
+      <c r="BC52" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -8143,7 +8288,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10">
@@ -8153,7 +8298,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11">
@@ -8205,7 +8350,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3932</v>
+        <v>3937</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d057/2026-2029.xlsx
+++ b/diseases/d057/2026-2029.xlsx
@@ -6354,13 +6354,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O40" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R40" t="n">
-        <v>0.05620112778996933</v>
+        <v>0.05426315786617728</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3937</v>
+        <v>3936</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d057/2026-2029.xlsx
+++ b/diseases/d057/2026-2029.xlsx
@@ -7185,12 +7185,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -7224,13 +7224,16 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>16</v>
+        <v>666</v>
       </c>
       <c r="O46" t="n">
-        <v>16</v>
+        <v>666</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>47</v>
       </c>
       <c r="R46" t="n">
-        <v>0.03100751878067274</v>
+        <v>0.04713662390521205</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -7263,42 +7266,42 @@
       </c>
       <c r="AV46" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC46" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7333,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -7360,7 +7363,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -7369,13 +7372,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="O47" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="R47" t="n">
-        <v>0.004084042037828832</v>
+        <v>0.03100751878067274</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -7408,42 +7411,42 @@
       </c>
       <c r="AV47" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB47" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC47" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -7505,7 +7508,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -7650,7 +7653,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -7659,13 +7662,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O49" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R49" t="n">
-        <v>0.002450425222697299</v>
+        <v>0.004084042037828832</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -7795,7 +7798,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -7940,7 +7943,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -7949,13 +7952,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O51" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R51" t="n">
-        <v>0.003267233630263065</v>
+        <v>0.002450425222697299</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -8055,12 +8058,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -8085,22 +8088,22 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O52" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R52" t="n">
-        <v>0.001937969923792046</v>
+        <v>0.003267233630263065</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -8133,40 +8136,185 @@
       </c>
       <c r="AV52" t="inlineStr">
         <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA52" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB52" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC52" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>D057</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>sfts</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>SFTS</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>D057</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>SFTS</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>发热伴血小板减少综合征</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>1</v>
+      </c>
+      <c r="O53" t="n">
+        <v>1</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0.001937969923792046</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP53" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr"/>
+      <c r="AT53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV53" t="inlineStr">
+        <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW52" t="inlineStr">
+      <c r="AW53" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
+      <c r="AX53" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY52" t="inlineStr">
+      <c r="AY53" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
+      <c r="AZ53" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA52" t="inlineStr">
+      <c r="BA53" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB52" t="inlineStr">
+      <c r="BB53" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC52" t="inlineStr">
+      <c r="BC53" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -8288,7 +8436,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10">
@@ -8298,7 +8446,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11">
@@ -8350,7 +8498,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3936</v>
+        <v>4602</v>
       </c>
     </row>
     <row r="16">
@@ -8360,7 +8508,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>182</v>
+        <v>229</v>
       </c>
     </row>
     <row r="17">

--- a/diseases/d057/2026-2029.xlsx
+++ b/diseases/d057/2026-2029.xlsx
@@ -8242,13 +8242,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R53" t="n">
-        <v>0.001937969923792046</v>
+        <v>0.003875939847584092</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -8317,6 +8317,151 @@
       <c r="BC53" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>D057</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>sfts</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>SFTS</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>D057</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>SFTS</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>发热伴血小板减少综合征</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>5</v>
+      </c>
+      <c r="O54" t="n">
+        <v>5</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0.004084042037828832</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP54" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS54" t="inlineStr"/>
+      <c r="AT54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV54" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA54" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB54" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC54" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -8353,7 +8498,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -8436,7 +8581,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10">
@@ -8446,7 +8591,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11">
@@ -8498,7 +8643,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4602</v>
+        <v>4608</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d057/2026-2029.xlsx
+++ b/diseases/d057/2026-2029.xlsx
@@ -7372,13 +7372,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O47" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R47" t="n">
-        <v>0.03100751878067274</v>
+        <v>0.02906954885688069</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4608</v>
+        <v>4607</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d057/2026-2029.xlsx
+++ b/diseases/d057/2026-2029.xlsx
@@ -6354,13 +6354,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="O40" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="R40" t="n">
-        <v>0.05426315786617728</v>
+        <v>0.06007706763755342</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -7372,13 +7372,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="O47" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="R47" t="n">
-        <v>0.02906954885688069</v>
+        <v>0.03682142855204888</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -8242,13 +8242,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O53" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R53" t="n">
-        <v>0.003875939847584092</v>
+        <v>0.01162781954275227</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4607</v>
+        <v>4618</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d057/2026-2029.xlsx
+++ b/diseases/d057/2026-2029.xlsx
@@ -8242,13 +8242,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="O53" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R53" t="n">
-        <v>0.01162781954275227</v>
+        <v>0.02325563908550455</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4618</v>
+        <v>4624</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d057/2026-2029.xlsx
+++ b/diseases/d057/2026-2029.xlsx
@@ -7372,13 +7372,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O47" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R47" t="n">
-        <v>0.03682142855204888</v>
+        <v>0.03875939847584092</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -8460,6 +8460,151 @@
         </is>
       </c>
       <c r="BC54" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>D057</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>sfts</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>SFTS</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>D057</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>SFTS</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>发热伴血小板减少综合征</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>4</v>
+      </c>
+      <c r="O55" t="n">
+        <v>4</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0.003267233630263065</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP55" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS55" t="inlineStr"/>
+      <c r="AT55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV55" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA55" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB55" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC55" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -8498,7 +8643,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -8581,7 +8726,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10">
@@ -8591,7 +8736,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11">
@@ -8643,7 +8788,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4624</v>
+        <v>4629</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d057/2026-2029.xlsx
+++ b/diseases/d057/2026-2029.xlsx
@@ -18382,13 +18382,13 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="O105" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="R105" t="n">
-        <v>0.02325563908550455</v>
+        <v>0.04844924809480115</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
@@ -18747,6 +18747,296 @@
       <c r="BC107" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>D057</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>sfts</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>SFTS</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>D057</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>SFTS</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>发热伴血小板减少综合征</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N108" t="n">
+        <v>3</v>
+      </c>
+      <c r="O108" t="n">
+        <v>3</v>
+      </c>
+      <c r="R108" t="n">
+        <v>0.002450425222697299</v>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP108" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR108" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS108" t="inlineStr"/>
+      <c r="AT108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU108" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV108" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA108" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB108" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC108" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>D057</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>sfts</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>SFTS</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>D057</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>SFTS</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>发热伴血小板减少综合征</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N109" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0</v>
+      </c>
+      <c r="R109" t="n">
+        <v>0</v>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP109" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR109" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS109" t="inlineStr"/>
+      <c r="AT109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU109" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV109" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA109" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB109" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC109" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -18783,7 +19073,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -18866,7 +19156,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10">
@@ -18876,7 +19166,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11">
@@ -18928,7 +19218,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5895</v>
+        <v>5911</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d057/2026-2029.xlsx
+++ b/diseases/d057/2026-2029.xlsx
@@ -18382,13 +18382,13 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O105" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R105" t="n">
-        <v>0.04844924809480115</v>
+        <v>0.05038721801859319</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
@@ -18923,12 +18923,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -18953,22 +18953,22 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O109" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R109" t="n">
-        <v>0</v>
+        <v>0.003267233630263065</v>
       </c>
       <c r="S109" t="inlineStr">
         <is>
@@ -19001,40 +19001,185 @@
       </c>
       <c r="AV109" t="inlineStr">
         <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA109" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB109" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC109" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>D057</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>sfts</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>SFTS</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>D057</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>SFTS</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>发热伴血小板减少综合征</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N110" t="n">
+        <v>1</v>
+      </c>
+      <c r="O110" t="n">
+        <v>1</v>
+      </c>
+      <c r="R110" t="n">
+        <v>0.001937969923792046</v>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP110" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR110" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS110" t="inlineStr"/>
+      <c r="AT110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU110" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV110" t="inlineStr">
+        <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW109" t="inlineStr">
+      <c r="AW110" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX109" t="inlineStr">
+      <c r="AX110" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY109" t="inlineStr">
+      <c r="AY110" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ109" t="inlineStr">
+      <c r="AZ110" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA109" t="inlineStr">
+      <c r="BA110" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB109" t="inlineStr">
+      <c r="BB110" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC109" t="inlineStr">
+      <c r="BC110" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -19156,7 +19301,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10">
@@ -19166,7 +19311,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11">
@@ -19218,7 +19363,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5911</v>
+        <v>5917</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d057/2026-2029.xlsx
+++ b/diseases/d057/2026-2029.xlsx
@@ -18382,13 +18382,13 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O105" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="R105" t="n">
-        <v>0.05038721801859319</v>
+        <v>0.05232518794238524</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
@@ -19107,13 +19107,13 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R110" t="n">
-        <v>0.001937969923792046</v>
+        <v>0.003875939847584092</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
@@ -19363,7 +19363,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5917</v>
+        <v>5919</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d057/2026-2029.xlsx
+++ b/diseases/d057/2026-2029.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -921,6 +926,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1661,6 +1671,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1806,6 +1821,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2546,6 +2566,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2691,6 +2716,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3431,6 +3461,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3576,6 +3611,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4316,6 +4356,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5241,6 +5286,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6129,6 +6179,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9394,6 +9449,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10122,6 +10182,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13777,6 +13842,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14650,6 +14720,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17525,6 +17600,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18395,6 +18475,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19107,17 +19192,22 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R110" t="n">
-        <v>0.003875939847584092</v>
+        <v>0.005813909771376137</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO110" t="inlineStr">
@@ -19363,7 +19453,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5919</v>
+        <v>5920</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d057/2026-2029.xlsx
+++ b/diseases/d057/2026-2029.xlsx
@@ -17587,13 +17587,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O99" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R99" t="n">
-        <v>0.03875939847584092</v>
+        <v>0.04069736839963296</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -18462,13 +18462,13 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O105" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R105" t="n">
-        <v>0.05232518794238524</v>
+        <v>0.05426315786617728</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
@@ -19192,13 +19192,13 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O110" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="R110" t="n">
-        <v>0.005813909771376137</v>
+        <v>0.01356578946654432</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
@@ -19453,7 +19453,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5920</v>
+        <v>5926</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d057/2026-2029.xlsx
+++ b/diseases/d057/2026-2029.xlsx
@@ -18462,13 +18462,13 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O105" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R105" t="n">
-        <v>0.05426315786617728</v>
+        <v>0.05620112778996933</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
@@ -19192,13 +19192,13 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="O110" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="R110" t="n">
-        <v>0.01356578946654432</v>
+        <v>0.02325563908550455</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
@@ -19272,6 +19272,151 @@
       <c r="BC110" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>D057</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>sfts</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>SFTS</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>D057</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>SFTS</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>发热伴血小板减少综合征</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N111" t="n">
+        <v>2</v>
+      </c>
+      <c r="O111" t="n">
+        <v>2</v>
+      </c>
+      <c r="R111" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO111" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP111" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR111" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS111" t="inlineStr"/>
+      <c r="AT111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU111" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV111" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA111" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB111" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC111" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -19308,7 +19453,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -19391,7 +19536,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10">
@@ -19401,7 +19546,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11">
@@ -19453,7 +19598,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5926</v>
+        <v>5934</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d057/2026-2029.xlsx
+++ b/diseases/d057/2026-2029.xlsx
@@ -17587,13 +17587,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O99" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="R99" t="n">
-        <v>0.04069736839963296</v>
+        <v>0.04457330824721705</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -18462,13 +18462,13 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="O105" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="R105" t="n">
-        <v>0.05620112778996933</v>
+        <v>0.06395300748513752</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
@@ -19192,13 +19192,13 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="O110" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="R110" t="n">
-        <v>0.02325563908550455</v>
+        <v>0.03100751878067274</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
@@ -19598,7 +19598,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5934</v>
+        <v>5944</v>
       </c>
     </row>
     <row r="16">
